--- a/scraper/downloads/yad2_page_3.xlsx
+++ b/scraper/downloads/yad2_page_3.xlsx
@@ -216,7 +216,7 @@
     <col min="13" max="13" width="12.15" customWidth="1"/>
     <col min="14" max="14" width="54" customWidth="1"/>
     <col min="15" max="15" width="13.5" customWidth="1"/>
-    <col min="16" max="16" width="51.300000000000004" customWidth="1"/>
+    <col min="16" max="16" width="25.650000000000002" customWidth="1"/>
     <col min="17" max="17" width="8.100000000000001" customWidth="1"/>
     <col min="18" max="18" width="6.75" customWidth="1"/>
     <col min="19" max="19" width="40.5" customWidth="1"/>
@@ -333,38 +333,36 @@
       </c>
       <c t="inlineStr" r="C3">
         <is>
-          <t xml:space="preserve">הנשיא השישי</t>
+          <t xml:space="preserve">הנביאים</t>
         </is>
       </c>
       <c r="D3" s="65">
-        <v>6</v>
-      </c>
-      <c t="inlineStr" r="E3">
-        <is>
-          <t xml:space="preserve">/62</t>
-        </is>
+        <v>45</v>
+      </c>
+      <c r="E3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F3">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דופלקס</t>
         </is>
       </c>
       <c r="G3" s="65">
-        <v>4</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H3">
         <is>
-          <t xml:space="preserve">100מ״ר</t>
+          <t xml:space="preserve">185מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I3">
         <is>
-          <t xml:space="preserve">מרפסת: 22מ״רמרפסת: 3.18מ״ר</t>
+          <t xml:space="preserve">מרפסת: 44מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J3">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K3">
@@ -374,11 +372,11 @@
       </c>
       <c t="inlineStr" r="N3">
         <is>
-          <t xml:space="preserve">אילת (מתווכת)(054) 337-7581</t>
-        </is>
-      </c>
-      <c r="O3" s="63">
-        <v>4498000</v>
+          <t xml:space="preserve">ברגר נפתלי19177515365</t>
+        </is>
+      </c>
+      <c r="O3" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R3">
         <is>
@@ -387,7 +385,7 @@
       </c>
       <c t="inlineStr" r="S3">
         <is>
-          <t xml:space="preserve">מנחם אוריאל11-02-2026</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -402,15 +400,15 @@
       </c>
       <c t="inlineStr" r="C4">
         <is>
-          <t xml:space="preserve">הנשיא שישי</t>
+          <t xml:space="preserve">הנשיא השישי</t>
         </is>
       </c>
       <c r="D4" s="65">
-        <v>14</v>
+        <v>6</v>
       </c>
       <c t="inlineStr" r="E4">
         <is>
-          <t xml:space="preserve">/86</t>
+          <t xml:space="preserve">/62</t>
         </is>
       </c>
       <c t="inlineStr" r="F4">
@@ -418,41 +416,36 @@
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="n" r="G4">
-        <v>2.5</v>
+      <c r="G4" s="65">
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H4">
         <is>
-          <t xml:space="preserve">69מ״ר</t>
+          <t xml:space="preserve">100מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I4">
         <is>
-          <t xml:space="preserve">מרפסת: 17מ״ר</t>
+          <t xml:space="preserve">מרפסת: 22מ״רמרפסת: 3.18מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J4">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K4">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M4">
-        <is>
-          <t xml:space="preserve">עורף</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N4">
         <is>
-          <t xml:space="preserve">ד"ר ירון אילן(050) 787-4551</t>
+          <t xml:space="preserve">אילת (מתווכת)(054) 337-7581</t>
         </is>
       </c>
       <c r="O4" s="63">
-        <v>3150000</v>
+        <v>4498000</v>
       </c>
       <c t="inlineStr" r="R4">
         <is>
@@ -461,7 +454,7 @@
       </c>
       <c t="inlineStr" r="S4">
         <is>
-          <t xml:space="preserve">אריה טאו24-12-2025</t>
+          <t xml:space="preserve">מנחם אוריאל11-02-2026</t>
         </is>
       </c>
     </row>
@@ -476,45 +469,57 @@
       </c>
       <c t="inlineStr" r="C5">
         <is>
-          <t xml:space="preserve">הצפירה</t>
+          <t xml:space="preserve">הנשיא שישי</t>
         </is>
       </c>
       <c r="D5" s="65">
-        <v>21</v>
-      </c>
-      <c r="E5" s="65">
-        <v>0</v>
+        <v>14</v>
+      </c>
+      <c t="inlineStr" r="E5">
+        <is>
+          <t xml:space="preserve">/86</t>
+        </is>
       </c>
       <c t="inlineStr" r="F5">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G5" s="65">
-        <v>0</v>
+      <c t="n" r="G5">
+        <v>2.5</v>
       </c>
       <c t="inlineStr" r="H5">
         <is>
-          <t xml:space="preserve">320מ״ר</t>
+          <t xml:space="preserve">69מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I5">
+        <is>
+          <t xml:space="preserve">מרפסת: 17מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J5">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K5">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M5">
+        <is>
+          <t xml:space="preserve">עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N5">
         <is>
-          <t xml:space="preserve">מייבון עוזי</t>
-        </is>
-      </c>
-      <c r="O5" s="65">
-        <v>0</v>
+          <t xml:space="preserve">ד"ר ירון אילן(050) 787-4551</t>
+        </is>
+      </c>
+      <c r="O5" s="63">
+        <v>3150000</v>
       </c>
       <c t="inlineStr" r="R5">
         <is>
@@ -523,7 +528,7 @@
       </c>
       <c t="inlineStr" r="S5">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">אריה טאו24-12-2025</t>
         </is>
       </c>
     </row>
@@ -538,16 +543,14 @@
       </c>
       <c t="inlineStr" r="C6">
         <is>
-          <t xml:space="preserve">הקליר</t>
+          <t xml:space="preserve">הצפירה</t>
         </is>
       </c>
       <c r="D6" s="65">
-        <v>32</v>
-      </c>
-      <c t="inlineStr" r="E6">
-        <is>
-          <t xml:space="preserve">/33</t>
-        </is>
+        <v>21</v>
+      </c>
+      <c r="E6" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F6">
         <is>
@@ -559,17 +562,12 @@
       </c>
       <c t="inlineStr" r="H6">
         <is>
-          <t xml:space="preserve">99מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I6">
-        <is>
-          <t xml:space="preserve">מרפסת: 6מ״ר</t>
+          <t xml:space="preserve">320מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J6">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K6">
@@ -577,18 +575,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L6">
-        <is>
-          <t xml:space="preserve">צפון מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N6">
         <is>
-          <t xml:space="preserve">פלד רחל(054) 434-7231</t>
-        </is>
-      </c>
-      <c r="O6" s="63">
-        <v>8300000</v>
+          <t xml:space="preserve">מייבון עוזי</t>
+        </is>
+      </c>
+      <c r="O6" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R6">
         <is>
@@ -597,7 +590,7 @@
       </c>
       <c t="inlineStr" r="S6">
         <is>
-          <t xml:space="preserve">אורן כהן26-08-2024</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -612,26 +605,28 @@
       </c>
       <c t="inlineStr" r="C7">
         <is>
-          <t xml:space="preserve">הקרן הקיימת</t>
+          <t xml:space="preserve">הקליר</t>
         </is>
       </c>
       <c r="D7" s="65">
-        <v>12</v>
-      </c>
-      <c r="E7" s="65">
-        <v>3</v>
+        <v>32</v>
+      </c>
+      <c t="inlineStr" r="E7">
+        <is>
+          <t xml:space="preserve">/33</t>
+        </is>
       </c>
       <c t="inlineStr" r="F7">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="n" r="G7">
-        <v>4.5</v>
+      <c r="G7" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H7">
         <is>
-          <t xml:space="preserve">130מ״ר</t>
+          <t xml:space="preserve">99מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I7">
@@ -641,7 +636,7 @@
       </c>
       <c t="inlineStr" r="J7">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K7">
@@ -651,16 +646,16 @@
       </c>
       <c t="inlineStr" r="L7">
         <is>
-          <t xml:space="preserve">דרום מזרח</t>
+          <t xml:space="preserve">צפון מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N7">
         <is>
-          <t xml:space="preserve">פיליפינית נטי(054) 658-3661</t>
+          <t xml:space="preserve">פלד רחל(054) 434-7231</t>
         </is>
       </c>
       <c r="O7" s="63">
-        <v>8200000</v>
+        <v>8300000</v>
       </c>
       <c t="inlineStr" r="R7">
         <is>
@@ -669,7 +664,7 @@
       </c>
       <c t="inlineStr" r="S7">
         <is>
-          <t xml:space="preserve">אורן כהן25-11-2024</t>
+          <t xml:space="preserve">אורן כהן26-08-2024</t>
         </is>
       </c>
     </row>
@@ -684,31 +679,36 @@
       </c>
       <c t="inlineStr" r="C8">
         <is>
-          <t xml:space="preserve">הקרן הקיימת לישראל</t>
+          <t xml:space="preserve">הקרן הקיימת</t>
         </is>
       </c>
       <c r="D8" s="65">
         <v>12</v>
       </c>
       <c r="E8" s="65">
-        <v>0</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="F8">
         <is>
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c r="G8" s="65">
-        <v>2</v>
+      <c t="n" r="G8">
+        <v>4.5</v>
       </c>
       <c t="inlineStr" r="H8">
         <is>
-          <t xml:space="preserve">72מ״ר</t>
+          <t xml:space="preserve">130מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I8">
+        <is>
+          <t xml:space="preserve">מרפסת: 6מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J8">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K8">
@@ -716,13 +716,18 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L8">
+        <is>
+          <t xml:space="preserve">דרום מזרח</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N8">
         <is>
-          <t xml:space="preserve">ברוך בלוי(052) 678-9111</t>
-        </is>
-      </c>
-      <c r="O8" s="65">
-        <v>0</v>
+          <t xml:space="preserve">פיליפינית נטי(054) 658-3661</t>
+        </is>
+      </c>
+      <c r="O8" s="63">
+        <v>8200000</v>
       </c>
       <c t="inlineStr" r="R8">
         <is>
@@ -731,7 +736,7 @@
       </c>
       <c t="inlineStr" r="S8">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">אורן כהן25-11-2024</t>
         </is>
       </c>
     </row>
@@ -746,14 +751,14 @@
       </c>
       <c t="inlineStr" r="C9">
         <is>
-          <t xml:space="preserve">הר"ן</t>
+          <t xml:space="preserve">הקרן הקיימת לישראל</t>
         </is>
       </c>
       <c r="D9" s="65">
-        <v>8</v>
+        <v>12</v>
       </c>
       <c r="E9" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F9">
         <is>
@@ -765,12 +770,7 @@
       </c>
       <c t="inlineStr" r="H9">
         <is>
-          <t xml:space="preserve">75מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I9">
-        <is>
-          <t xml:space="preserve">מרפסת: 2מ״ר</t>
+          <t xml:space="preserve">72מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J9">
@@ -785,7 +785,7 @@
       </c>
       <c t="inlineStr" r="N9">
         <is>
-          <t xml:space="preserve">לאה שרה</t>
+          <t xml:space="preserve">ברוך בלוי(052) 678-9111</t>
         </is>
       </c>
       <c r="O9" s="65">
@@ -798,7 +798,7 @@
       </c>
       <c t="inlineStr" r="S9">
         <is>
-          <t xml:space="preserve">משה קולטון04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -813,16 +813,14 @@
       </c>
       <c t="inlineStr" r="C10">
         <is>
-          <t xml:space="preserve">הרב חיים ברלין</t>
+          <t xml:space="preserve">הר"ן</t>
         </is>
       </c>
       <c r="D10" s="65">
-        <v>30</v>
-      </c>
-      <c t="inlineStr" r="E10">
-        <is>
-          <t xml:space="preserve">/21</t>
-        </is>
+        <v>8</v>
+      </c>
+      <c r="E10" s="65">
+        <v>1</v>
       </c>
       <c t="inlineStr" r="F10">
         <is>
@@ -830,30 +828,35 @@
         </is>
       </c>
       <c r="G10" s="65">
-        <v>3</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H10">
         <is>
-          <t xml:space="preserve">66.6מ״ר</t>
+          <t xml:space="preserve">75מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I10">
         <is>
-          <t xml:space="preserve">מרפסת: 3מ״ר</t>
+          <t xml:space="preserve">מרפסת: 2מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J10">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K10">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c r="O10" s="63">
-        <v>3700000</v>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="N10">
+        <is>
+          <t xml:space="preserve">לאה שרה</t>
+        </is>
+      </c>
+      <c r="O10" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R10">
         <is>
@@ -862,7 +865,7 @@
       </c>
       <c t="inlineStr" r="S10">
         <is>
-          <t xml:space="preserve">דוב רבינובץ\'08-06-2026</t>
+          <t xml:space="preserve">משה קולטון04-11-2024</t>
         </is>
       </c>
     </row>
@@ -877,18 +880,20 @@
       </c>
       <c t="inlineStr" r="C11">
         <is>
-          <t xml:space="preserve">הרן</t>
+          <t xml:space="preserve">הרב חיים ברלין</t>
         </is>
       </c>
       <c r="D11" s="65">
-        <v>18</v>
-      </c>
-      <c r="E11" s="65">
-        <v>0</v>
+        <v>30</v>
+      </c>
+      <c t="inlineStr" r="E11">
+        <is>
+          <t xml:space="preserve">/21</t>
+        </is>
       </c>
       <c t="inlineStr" r="F11">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G11" s="65">
@@ -896,31 +901,26 @@
       </c>
       <c t="inlineStr" r="H11">
         <is>
-          <t xml:space="preserve">59מ״ר</t>
+          <t xml:space="preserve">66.6מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I11">
         <is>
-          <t xml:space="preserve">גינה: 40מ״ר</t>
+          <t xml:space="preserve">מרפסת: 3מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J11">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K11">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N11">
-        <is>
-          <t xml:space="preserve">יובל בורנשטיין(054) 777-0161</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c r="O11" s="63">
-        <v>4950000</v>
+        <v>3700000</v>
       </c>
       <c t="inlineStr" r="R11">
         <is>
@@ -929,7 +929,7 @@
       </c>
       <c t="inlineStr" r="S11">
         <is>
-          <t xml:space="preserve">רבקה בן זקן13-12-2025</t>
+          <t xml:space="preserve">דוב רבינובץ\'08-06-2026</t>
         </is>
       </c>
     </row>
@@ -944,33 +944,31 @@
       </c>
       <c t="inlineStr" r="C12">
         <is>
-          <t xml:space="preserve">השוערים</t>
+          <t xml:space="preserve">הרן</t>
         </is>
       </c>
       <c r="D12" s="65">
-        <v>5</v>
-      </c>
-      <c t="inlineStr" r="E12">
-        <is>
-          <t xml:space="preserve">/31</t>
-        </is>
+        <v>18</v>
+      </c>
+      <c r="E12" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F12">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דירת גן</t>
         </is>
       </c>
       <c r="G12" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H12">
         <is>
-          <t xml:space="preserve">118מ״ר</t>
+          <t xml:space="preserve">59מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I12">
         <is>
-          <t xml:space="preserve">מרפסת: 23.76מ״רמרפסת: 42.52מ״רמרפסת: 50.16מ״ר</t>
+          <t xml:space="preserve">גינה: 40מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J12">
@@ -983,23 +981,13 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L12">
-        <is>
-          <t xml:space="preserve">דרום מזרח</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M12">
-        <is>
-          <t xml:space="preserve">עורף</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N12">
         <is>
-          <t xml:space="preserve">תמר בן שושןמתניה צמח - איש הקשר052-5448445</t>
+          <t xml:space="preserve">יובל בורנשטיין(054) 777-0161</t>
         </is>
       </c>
       <c r="O12" s="63">
-        <v>19000000</v>
+        <v>4950000</v>
       </c>
       <c t="inlineStr" r="R12">
         <is>
@@ -1008,7 +996,7 @@
       </c>
       <c t="inlineStr" r="S12">
         <is>
-          <t xml:space="preserve">מנחם אוריאל11-08-2025</t>
+          <t xml:space="preserve">רבקה בן זקן13-12-2025</t>
         </is>
       </c>
     </row>
@@ -1023,14 +1011,16 @@
       </c>
       <c t="inlineStr" r="C13">
         <is>
-          <t xml:space="preserve">התקופה</t>
+          <t xml:space="preserve">השוערים</t>
         </is>
       </c>
       <c r="D13" s="65">
-        <v>4</v>
-      </c>
-      <c r="E13" s="65">
-        <v>0</v>
+        <v>5</v>
+      </c>
+      <c t="inlineStr" r="E13">
+        <is>
+          <t xml:space="preserve">/31</t>
+        </is>
       </c>
       <c t="inlineStr" r="F13">
         <is>
@@ -1042,7 +1032,12 @@
       </c>
       <c t="inlineStr" r="H13">
         <is>
-          <t xml:space="preserve">2210מ״ר</t>
+          <t xml:space="preserve">118מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I13">
+        <is>
+          <t xml:space="preserve">מרפסת: 23.76מ״רמרפסת: 42.52מ״רמרפסת: 50.16מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J13">
@@ -1055,13 +1050,23 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L13">
+        <is>
+          <t xml:space="preserve">דרום מזרח</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M13">
+        <is>
+          <t xml:space="preserve">עורף</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N13">
         <is>
-          <t xml:space="preserve">שלמה ואסתי לקס</t>
-        </is>
-      </c>
-      <c r="O13" s="65">
-        <v>0</v>
+          <t xml:space="preserve">תמר בן שושןמתניה צמח - איש הקשר052-5448445</t>
+        </is>
+      </c>
+      <c r="O13" s="63">
+        <v>19000000</v>
       </c>
       <c t="inlineStr" r="R13">
         <is>
@@ -1070,7 +1075,7 @@
       </c>
       <c t="inlineStr" r="S13">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל11-08-2025</t>
         </is>
       </c>
     </row>
@@ -1085,11 +1090,11 @@
       </c>
       <c t="inlineStr" r="C14">
         <is>
-          <t xml:space="preserve">חבד</t>
+          <t xml:space="preserve">התקופה</t>
         </is>
       </c>
       <c r="D14" s="65">
-        <v>68</v>
+        <v>4</v>
       </c>
       <c r="E14" s="65">
         <v>0</v>
@@ -1100,11 +1105,11 @@
         </is>
       </c>
       <c r="G14" s="65">
-        <v>0</v>
+        <v>5</v>
       </c>
       <c t="inlineStr" r="H14">
         <is>
-          <t xml:space="preserve">84מ״ר</t>
+          <t xml:space="preserve">2210מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J14">
@@ -1119,11 +1124,11 @@
       </c>
       <c t="inlineStr" r="N14">
         <is>
-          <t xml:space="preserve">הרב חיים כהנא(058) 762-9743</t>
+          <t xml:space="preserve">שלמה ואסתי לקס</t>
         </is>
       </c>
       <c r="O14" s="65">
-        <v>1</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R14">
         <is>
@@ -1132,7 +1137,7 @@
       </c>
       <c t="inlineStr" r="S14">
         <is>
-          <t xml:space="preserve">מנחם אוריאל17-02-2026</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1147,11 +1152,11 @@
       </c>
       <c t="inlineStr" r="C15">
         <is>
-          <t xml:space="preserve">חובבי ציון</t>
+          <t xml:space="preserve">חבד</t>
         </is>
       </c>
       <c r="D15" s="65">
-        <v>27</v>
+        <v>68</v>
       </c>
       <c r="E15" s="65">
         <v>0</v>
@@ -1162,11 +1167,11 @@
         </is>
       </c>
       <c r="G15" s="65">
-        <v>2</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H15">
         <is>
-          <t xml:space="preserve">75מ״ר</t>
+          <t xml:space="preserve">84מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J15">
@@ -1181,11 +1186,11 @@
       </c>
       <c t="inlineStr" r="N15">
         <is>
-          <t xml:space="preserve">ישראל(058) 500-2312</t>
+          <t xml:space="preserve">הרב חיים כהנא(058) 762-9743</t>
         </is>
       </c>
       <c r="O15" s="65">
-        <v>0</v>
+        <v>1</v>
       </c>
       <c t="inlineStr" r="R15">
         <is>
@@ -1194,7 +1199,7 @@
       </c>
       <c t="inlineStr" r="S15">
         <is>
-          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
+          <t xml:space="preserve">מנחם אוריאל17-02-2026</t>
         </is>
       </c>
     </row>
@@ -1277,7 +1282,7 @@
         </is>
       </c>
       <c r="D17" s="65">
-        <v>9</v>
+        <v>27</v>
       </c>
       <c r="E17" s="65">
         <v>0</v>
@@ -1288,11 +1293,11 @@
         </is>
       </c>
       <c r="G17" s="65">
-        <v>0</v>
+        <v>2</v>
       </c>
       <c t="inlineStr" r="H17">
         <is>
-          <t xml:space="preserve">0מ״ר</t>
+          <t xml:space="preserve">75מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J17">
@@ -1307,7 +1312,7 @@
       </c>
       <c t="inlineStr" r="N17">
         <is>
-          <t xml:space="preserve">פרייגין גארי</t>
+          <t xml:space="preserve">ישראל(058) 500-2312</t>
         </is>
       </c>
       <c r="O17" s="65">
@@ -1320,7 +1325,7 @@
       </c>
       <c t="inlineStr" r="S17">
         <is>
-          <t xml:space="preserve">אורן כהן04-11-2024</t>
+          <t xml:space="preserve">רבקה בן זקן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1335,18 +1340,18 @@
       </c>
       <c t="inlineStr" r="C18">
         <is>
-          <t xml:space="preserve">חיל נשים</t>
+          <t xml:space="preserve">חובבי ציון</t>
         </is>
       </c>
       <c r="D18" s="65">
-        <v>6</v>
+        <v>9</v>
       </c>
       <c r="E18" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F18">
         <is>
-          <t xml:space="preserve">דופלקס/פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G18" s="65">
@@ -1354,7 +1359,7 @@
       </c>
       <c t="inlineStr" r="H18">
         <is>
-          <t xml:space="preserve">300מ״ר</t>
+          <t xml:space="preserve">0מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J18">
@@ -1369,11 +1374,11 @@
       </c>
       <c t="inlineStr" r="N18">
         <is>
-          <t xml:space="preserve">דבלניגר גרופ בעמיעקב נטע בק(052) 769-4884</t>
-        </is>
-      </c>
-      <c r="O18" s="63">
-        <v>50000000</v>
+          <t xml:space="preserve">פרייגין גארי</t>
+        </is>
+      </c>
+      <c r="O18" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="R18">
         <is>
@@ -1382,7 +1387,7 @@
       </c>
       <c t="inlineStr" r="S18">
         <is>
-          <t xml:space="preserve">אורן כהן07-05-2025</t>
+          <t xml:space="preserve">אורן כהן04-11-2024</t>
         </is>
       </c>
     </row>
@@ -1397,33 +1402,26 @@
       </c>
       <c t="inlineStr" r="C19">
         <is>
-          <t xml:space="preserve">חנוך אלבק</t>
+          <t xml:space="preserve">חיל נשים</t>
         </is>
       </c>
       <c r="D19" s="65">
-        <v>15</v>
-      </c>
-      <c t="inlineStr" r="E19">
-        <is>
-          <t xml:space="preserve">/55</t>
-        </is>
+        <v>6</v>
+      </c>
+      <c r="E19" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F19">
         <is>
-          <t xml:space="preserve">דירה</t>
+          <t xml:space="preserve">דופלקס/פנטהאוז</t>
         </is>
       </c>
       <c r="G19" s="65">
-        <v>4</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H19">
         <is>
-          <t xml:space="preserve">90.9מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I19">
-        <is>
-          <t xml:space="preserve">מרפסת: 11.5מ״ר</t>
+          <t xml:space="preserve">300מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J19">
@@ -1433,26 +1431,16 @@
       </c>
       <c t="inlineStr" r="K19">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L19">
-        <is>
-          <t xml:space="preserve">צפון דרום מערב</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="M19">
-        <is>
-          <t xml:space="preserve">חזית</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N19">
         <is>
-          <t xml:space="preserve">שחר נתנאל(050) 777-4151לירז נתנאל(050) 527-8976</t>
+          <t xml:space="preserve">דבלניגר גרופ בעמיעקב נטע בק(052) 769-4884</t>
         </is>
       </c>
       <c r="O19" s="63">
-        <v>4270000</v>
+        <v>50000000</v>
       </c>
       <c t="inlineStr" r="R19">
         <is>
@@ -1461,7 +1449,7 @@
       </c>
       <c t="inlineStr" r="S19">
         <is>
-          <t xml:space="preserve">אריה טאו16-02-2026</t>
+          <t xml:space="preserve">אורן כהן07-05-2025</t>
         </is>
       </c>
     </row>
@@ -1476,15 +1464,15 @@
       </c>
       <c t="inlineStr" r="C20">
         <is>
-          <t xml:space="preserve">חרל"פ</t>
+          <t xml:space="preserve">חנוך אלבק</t>
         </is>
       </c>
       <c r="D20" s="65">
-        <v>34</v>
+        <v>15</v>
       </c>
       <c t="inlineStr" r="E20">
         <is>
-          <t xml:space="preserve">/42</t>
+          <t xml:space="preserve">/55</t>
         </is>
       </c>
       <c t="inlineStr" r="F20">
@@ -1492,12 +1480,17 @@
           <t xml:space="preserve">דירה</t>
         </is>
       </c>
-      <c t="n" r="G20">
-        <v>4.5</v>
+      <c r="G20" s="65">
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H20">
         <is>
-          <t xml:space="preserve">139.45מ״ר</t>
+          <t xml:space="preserve">90.9מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I20">
+        <is>
+          <t xml:space="preserve">מרפסת: 11.5מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J20">
@@ -1507,26 +1500,26 @@
       </c>
       <c t="inlineStr" r="K20">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L20">
         <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+          <t xml:space="preserve">צפון דרום מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="M20">
         <is>
-          <t xml:space="preserve">חזית עורף</t>
+          <t xml:space="preserve">חזית</t>
         </is>
       </c>
       <c t="inlineStr" r="N20">
         <is>
-          <t xml:space="preserve">דרור פאוול(054) 334-3342</t>
+          <t xml:space="preserve">שחר נתנאל(050) 777-4151לירז נתנאל(050) 527-8976</t>
         </is>
       </c>
       <c r="O20" s="63">
-        <v>6150000</v>
+        <v>4270000</v>
       </c>
       <c t="inlineStr" r="R20">
         <is>
@@ -1535,7 +1528,7 @@
       </c>
       <c t="inlineStr" r="S20">
         <is>
-          <t xml:space="preserve">אריה טאו16-10-2025</t>
+          <t xml:space="preserve">אריה טאו16-02-2026</t>
         </is>
       </c>
     </row>
@@ -1550,45 +1543,57 @@
       </c>
       <c t="inlineStr" r="C21">
         <is>
-          <t xml:space="preserve">טורא</t>
+          <t xml:space="preserve">חרל"פ</t>
         </is>
       </c>
       <c r="D21" s="65">
-        <v>40</v>
-      </c>
-      <c r="E21" s="65">
-        <v>0</v>
+        <v>34</v>
+      </c>
+      <c t="inlineStr" r="E21">
+        <is>
+          <t xml:space="preserve">/42</t>
+        </is>
       </c>
       <c t="inlineStr" r="F21">
         <is>
-          <t xml:space="preserve">בית פרטי</t>
-        </is>
-      </c>
-      <c r="G21" s="65">
-        <v>0</v>
+          <t xml:space="preserve">דירה</t>
+        </is>
+      </c>
+      <c t="n" r="G21">
+        <v>4.5</v>
       </c>
       <c t="inlineStr" r="H21">
         <is>
-          <t xml:space="preserve">457מ״ר</t>
+          <t xml:space="preserve">139.45מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J21">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K21">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
+          <t xml:space="preserve">ללא מחסן</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="L21">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M21">
+        <is>
+          <t xml:space="preserve">חזית עורף</t>
         </is>
       </c>
       <c t="inlineStr" r="N21">
         <is>
-          <t xml:space="preserve">פרוספריטי נדלן שת"פ</t>
+          <t xml:space="preserve">דרור פאוול(054) 334-3342</t>
         </is>
       </c>
       <c r="O21" s="63">
-        <v>80000000</v>
+        <v>6150000</v>
       </c>
       <c t="inlineStr" r="R21">
         <is>
@@ -1597,7 +1602,7 @@
       </c>
       <c t="inlineStr" r="S21">
         <is>
-          <t xml:space="preserve">אורן כהן24-06-2025</t>
+          <t xml:space="preserve">אריה טאו16-10-2025</t>
         </is>
       </c>
     </row>
@@ -1612,38 +1617,31 @@
       </c>
       <c t="inlineStr" r="C22">
         <is>
-          <t xml:space="preserve">טשרניחובסקי</t>
+          <t xml:space="preserve">טורא</t>
         </is>
       </c>
       <c r="D22" s="65">
-        <v>72</v>
-      </c>
-      <c t="inlineStr" r="E22">
-        <is>
-          <t xml:space="preserve">/1111</t>
-        </is>
+        <v>40</v>
+      </c>
+      <c r="E22" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F22">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">בית פרטי</t>
         </is>
       </c>
       <c r="G22" s="65">
-        <v>7</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H22">
         <is>
-          <t xml:space="preserve">200מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I22">
-        <is>
-          <t xml:space="preserve">מרפסת: 200מ״ר</t>
+          <t xml:space="preserve">457מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J22">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K22">
@@ -1651,18 +1649,13 @@
           <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
-      <c t="inlineStr" r="L22">
-        <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
-        </is>
-      </c>
       <c t="inlineStr" r="N22">
         <is>
-          <t xml:space="preserve">שמחה פלוטשניק(054) 844-9668אריה אלתר(053) 313-4646</t>
+          <t xml:space="preserve">פרוספריטי נדלן שת"פ</t>
         </is>
       </c>
       <c r="O22" s="63">
-        <v>13200000</v>
+        <v>80000000</v>
       </c>
       <c t="inlineStr" r="R22">
         <is>
@@ -1671,7 +1664,7 @@
       </c>
       <c t="inlineStr" r="S22">
         <is>
-          <t xml:space="preserve">אלחנן רווח29-07-2024</t>
+          <t xml:space="preserve">אורן כהן24-06-2025</t>
         </is>
       </c>
     </row>
@@ -1703,26 +1696,26 @@
         </is>
       </c>
       <c r="G23" s="65">
-        <v>4</v>
+        <v>7</v>
       </c>
       <c t="inlineStr" r="H23">
         <is>
-          <t xml:space="preserve">100מ״ר</t>
+          <t xml:space="preserve">200מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I23">
         <is>
-          <t xml:space="preserve">מרפסת: 100מ״ר</t>
+          <t xml:space="preserve">מרפסת: 200מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J23">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">2חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K23">
         <is>
-          <t xml:space="preserve">ללא מחסן</t>
+          <t xml:space="preserve">יש מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="L23">
@@ -1730,13 +1723,13 @@
           <t xml:space="preserve">צפון דרום מזרח מערב</t>
         </is>
       </c>
+      <c t="inlineStr" r="N23">
+        <is>
+          <t xml:space="preserve">שמחה פלוטשניק(054) 844-9668אריה אלתר(053) 313-4646</t>
+        </is>
+      </c>
       <c r="O23" s="63">
-        <v>6500000</v>
-      </c>
-      <c t="inlineStr" r="P23">
-        <is>
-          <t xml:space="preserve">מעליתבניין חדשאלחנן</t>
-        </is>
+        <v>13200000</v>
       </c>
       <c t="inlineStr" r="R23">
         <is>
@@ -1760,22 +1753,24 @@
       </c>
       <c t="inlineStr" r="C24">
         <is>
-          <t xml:space="preserve">יהודה</t>
+          <t xml:space="preserve">טשרניחובסקי</t>
         </is>
       </c>
       <c r="D24" s="65">
-        <v>7</v>
-      </c>
-      <c r="E24" s="65">
-        <v>0</v>
+        <v>72</v>
+      </c>
+      <c t="inlineStr" r="E24">
+        <is>
+          <t xml:space="preserve">/1111</t>
+        </is>
       </c>
       <c t="inlineStr" r="F24">
         <is>
-          <t xml:space="preserve">דירת גן</t>
+          <t xml:space="preserve">פנטהאוז</t>
         </is>
       </c>
       <c r="G24" s="65">
-        <v>0</v>
+        <v>4</v>
       </c>
       <c t="inlineStr" r="H24">
         <is>
@@ -1784,7 +1779,7 @@
       </c>
       <c t="inlineStr" r="I24">
         <is>
-          <t xml:space="preserve">גינה: 301מ״ר</t>
+          <t xml:space="preserve">מרפסת: 100מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J24">
@@ -1802,18 +1797,13 @@
           <t xml:space="preserve">צפון דרום מזרח מערב</t>
         </is>
       </c>
-      <c t="inlineStr" r="M24">
-        <is>
-          <t xml:space="preserve">חזית</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="N24">
-        <is>
-          <t xml:space="preserve">אילון קומבור(054) 313-1410</t>
-        </is>
-      </c>
       <c r="O24" s="63">
-        <v>11550000</v>
+        <v>6500000</v>
+      </c>
+      <c t="inlineStr" r="P24">
+        <is>
+          <t xml:space="preserve">מעליתבניין חדשאלחנן</t>
+        </is>
       </c>
       <c t="inlineStr" r="R24">
         <is>
@@ -1822,7 +1812,7 @@
       </c>
       <c t="inlineStr" r="S24">
         <is>
-          <t xml:space="preserve">אורן כהן13-08-2025</t>
+          <t xml:space="preserve">אלחנן רווח29-07-2024</t>
         </is>
       </c>
     </row>
@@ -1837,31 +1827,36 @@
       </c>
       <c t="inlineStr" r="C25">
         <is>
-          <t xml:space="preserve">יהושע בן נון</t>
+          <t xml:space="preserve">יהודה</t>
         </is>
       </c>
       <c r="D25" s="65">
-        <v>9</v>
+        <v>7</v>
       </c>
       <c r="E25" s="65">
         <v>0</v>
       </c>
       <c t="inlineStr" r="F25">
         <is>
-          <t xml:space="preserve">דופלקס</t>
-        </is>
-      </c>
-      <c t="n" r="G25">
-        <v>5.5</v>
+          <t xml:space="preserve">דירת גן</t>
+        </is>
+      </c>
+      <c r="G25" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="H25">
         <is>
-          <t xml:space="preserve">135מ״ר</t>
+          <t xml:space="preserve">100מ״ר</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="I25">
+        <is>
+          <t xml:space="preserve">גינה: 301מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J25">
         <is>
-          <t xml:space="preserve">ללא חניה</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K25">
@@ -1869,13 +1864,23 @@
           <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
+      <c t="inlineStr" r="L25">
+        <is>
+          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+        </is>
+      </c>
+      <c t="inlineStr" r="M25">
+        <is>
+          <t xml:space="preserve">חזית</t>
+        </is>
+      </c>
       <c t="inlineStr" r="N25">
         <is>
-          <t xml:space="preserve">רחל פטינקין - מתווכת054-5468732</t>
+          <t xml:space="preserve">אילון קומבור(054) 313-1410</t>
         </is>
       </c>
       <c r="O25" s="63">
-        <v>6350000</v>
+        <v>11550000</v>
       </c>
       <c t="inlineStr" r="R25">
         <is>
@@ -1884,7 +1889,7 @@
       </c>
       <c t="inlineStr" r="S25">
         <is>
-          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
+          <t xml:space="preserve">אורן כהן13-08-2025</t>
         </is>
       </c>
     </row>
@@ -1899,57 +1904,45 @@
       </c>
       <c t="inlineStr" r="C26">
         <is>
-          <t xml:space="preserve">יפו</t>
+          <t xml:space="preserve">יהושע בן נון</t>
         </is>
       </c>
       <c r="D26" s="65">
-        <v>0</v>
-      </c>
-      <c t="inlineStr" r="E26">
-        <is>
-          <t xml:space="preserve">/3118</t>
-        </is>
+        <v>9</v>
+      </c>
+      <c r="E26" s="65">
+        <v>0</v>
       </c>
       <c t="inlineStr" r="F26">
         <is>
-          <t xml:space="preserve">דירה</t>
-        </is>
-      </c>
-      <c r="G26" s="65">
-        <v>3</v>
+          <t xml:space="preserve">דופלקס</t>
+        </is>
+      </c>
+      <c t="n" r="G26">
+        <v>5.5</v>
       </c>
       <c t="inlineStr" r="H26">
         <is>
-          <t xml:space="preserve">82מ״ר</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="I26">
-        <is>
-          <t xml:space="preserve">מרפסת: 12מ״ר</t>
+          <t xml:space="preserve">135מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J26">
         <is>
-          <t xml:space="preserve">1חניות</t>
+          <t xml:space="preserve">ללא חניה</t>
         </is>
       </c>
       <c t="inlineStr" r="K26">
         <is>
-          <t xml:space="preserve">יש מחסן</t>
-        </is>
-      </c>
-      <c t="inlineStr" r="L26">
-        <is>
-          <t xml:space="preserve">מזרח מערב</t>
+          <t xml:space="preserve">ללא מחסן</t>
         </is>
       </c>
       <c t="inlineStr" r="N26">
         <is>
-          <t xml:space="preserve">ישראל פאוסט(052) 206-2760הינדי יעקובסון</t>
+          <t xml:space="preserve">רחל פטינקין - מתווכת054-5468732</t>
         </is>
       </c>
       <c r="O26" s="63">
-        <v>5600000</v>
+        <v>6350000</v>
       </c>
       <c t="inlineStr" r="R26">
         <is>
@@ -1958,7 +1951,7 @@
       </c>
       <c t="inlineStr" r="S26">
         <is>
-          <t xml:space="preserve">משה קולטון28-05-2025</t>
+          <t xml:space="preserve">מנחם אוריאל12-02-2026</t>
         </is>
       </c>
     </row>
@@ -1977,34 +1970,34 @@
         </is>
       </c>
       <c r="D27" s="65">
-        <v>180</v>
+        <v>0</v>
       </c>
       <c t="inlineStr" r="E27">
         <is>
-          <t xml:space="preserve">/1313</t>
+          <t xml:space="preserve">/3118</t>
         </is>
       </c>
       <c t="inlineStr" r="F27">
         <is>
-          <t xml:space="preserve">פנטהאוז</t>
+          <t xml:space="preserve">דירה</t>
         </is>
       </c>
       <c r="G27" s="65">
-        <v>5</v>
+        <v>3</v>
       </c>
       <c t="inlineStr" r="H27">
         <is>
-          <t xml:space="preserve">187מ״ר</t>
+          <t xml:space="preserve">82מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="I27">
         <is>
-          <t xml:space="preserve">מרפסת: 7.42מ״רמרפסת: 8.27מ״ר</t>
+          <t xml:space="preserve">מרפסת: 12מ״ר</t>
         </is>
       </c>
       <c t="inlineStr" r="J27">
         <is>
-          <t xml:space="preserve">2חניות</t>
+          <t xml:space="preserve">1חניות</t>
         </is>
       </c>
       <c t="inlineStr" r="K27">
@@ -2014,21 +2007,16 @@
       </c>
       <c t="inlineStr" r="L27">
         <is>
-          <t xml:space="preserve">צפון דרום מזרח מערב</t>
+          <t xml:space="preserve">מזרח מערב</t>
         </is>
       </c>
       <c t="inlineStr" r="N27">
         <is>
-          <t xml:space="preserve">משה בר עמי(054) 220-5522בועז הר עמי(054) 770-3070</t>
+          <t xml:space="preserve">ישראל פאוסט(052) 206-2760הינדי יעקובסון</t>
         </is>
       </c>
       <c r="O27" s="63">
-        <v>18500000</v>
-      </c>
-      <c t="inlineStr" r="P27">
-        <is>
-          <t xml:space="preserve">מיזוגמעליתממ״דאלחנןגישה לנכיםבניין חדש</t>
-        </is>
+        <v>5600000</v>
       </c>
       <c t="inlineStr" r="R27">
         <is>
@@ -2037,7 +2025,7 @@
       </c>
       <c t="inlineStr" r="S27">
         <is>
-          <t xml:space="preserve">אלחנן רווח16-07-2024</t>
+          <t xml:space="preserve">משה קולטון28-05-2025</t>
         </is>
       </c>
     </row>
